--- a/public/business-plans/it.xlsx
+++ b/public/business-plans/it.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,10 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
@@ -66,12 +70,17 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,19 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +570,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Информационные технологии и связь (IT)». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
+          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Информационные технологии и связь (IT)». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Абзацы, отмеченные как «ПРИМЕР», — иллюстрация формата ответа, а не факты о реальной компании; замените их своими данными. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -592,31 +604,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="89" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Студия разработки «CodeVodiy» специализируется на аутсорсинговой разработке мобильных приложений для европейских клиентов, зарегистрирована резидентом IT Park. Требуемые инвестиции — 300 млн сум на первые 3 месяца работы команды из 6 человек до выхода на устойчивый поток проектов; окупаемость — около 8 месяцев при загрузке команды на 2 параллельных проекта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] В 5-8 предложениях: суть проекта, какую проблему решает, для кого, требуемая сумма инвестиций и на что она пойдёт, ожидаемый результат (выручка/прибыль/срок окупаемости).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Описание компании / проекта</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Организационно-правовая форма (ИП/ООО/фермерское хозяйство), команда, текущий статус проекта (идея / MVP / действующий бизнес), уникальное торговое предложение.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -628,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -641,68 +661,84 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="59" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>•  IT Park Uzbekistan даёт резидентам налоговые льготы (в т.ч. на экспорт IT-услуг) — стоит изучить условия регистрации резидентом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>•  IT Park Uzbekistan даёт резидентам налоговые льготы (в т.ч. освобождение от налога на прибыль для компаний-экспортёров с объёмом экспорта свыше $10 млн) — стоит изучить актуальные условия регистрации резидентом (uz24.uz, it-park.uz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="74" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>•  Растёт IT-экспорт из Узбекистана — аутсорсинг разработки для рынков США, ЕС и СНГ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>•  Резидентская база IT Park быстро растёт: по данным Spot.uz, с начала 2025 года резидентами стали 636 новых компаний; по данным самого IT Park, только за 7 месяцев 2025 года присоединились 481 новый экспортёр и 232 иностранные компании — конкуренция за кадры и клиентов в резидентском пуле усиливается (spot.uz, it-park.uz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>•  Дефицит квалифицированных разработчиков создаёт конкуренцию за кадры и давление на зарплаты в отрасли.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>•  Растёт IT-экспорт из Узбекистана — аутсорсинг разработки для рынков США, ЕС и СНГ остаётся основной моделью для большинства резидентов IT Park, наряду с растущим числом продуктовых/SaaS-компаний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>•  [Впишите] Целевую нишу (аутсорсинг/продукт/SaaS), конкурентов и их ценообразование.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Конкуренты</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+          <t>•  Дефицит квалифицированных разработчиков создаёт конкуренцию за кадры и давление на зарплаты в отрасли — при планировании ФОТ ориентируйтесь на текущий рынок труда, а не на данные прошлых лет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="74" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>•  Для сравнения: Грузия и Армения также активно привлекают IT-компании налоговыми льготами и визовыми режимами и конкурируют с Узбекистаном за относительно мобильные команды разработки на аутсорсе — для удержания кадров важны не только зарплата, но и условия (удалёнка, релокационные пакеты, обучение).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>•  [Впишите] Целевую нишу (аутсорсинг/продукт/SaaS/маркетплейс), конкурентов и их ценообразование — уточняйте по отраслевым обзорам IT Park и профильным сообществам разработчиков.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Целевая аудитория</t>
+          <t>Конкуренты</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Целевая аудитория</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
@@ -716,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -729,117 +765,183 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="59" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цена — по модели time &amp; material, на 20-30% ниже европейских студий сопоставимого уровня; продвижение — профиль на Clutch/Upwork, портфолио кейсов, партнёрство с 1-2 зарубежными IT-агентствами для субподряда на первых проектах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Ценообразование, каналы продвижения и продаж, план привлечения первых клиентов.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Операционный план</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="74" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цикл: квалификация лида → оценка и коммерческое предложение → разработка спринтами (Scrum) → сдача этапов заказчику → поддержка после релиза. Ключевая инфраструктура — облачный хостинг, лицензии на инструменты разработки. Требуется регистрация резидентом IT Park для налоговых льгот.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Процесс производства/оказания услуги, ключевые поставщики, оборудование, необходимые лицензии и разрешения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Организационный план</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Организационный план</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Тимлид-основатель, 4 разработчика, QA-инженер, менеджер проектов на part-time, бухгалтер на аутсорсе. Форма — ООО, резидент IT Park (специальный налоговый режим для IT-экспортёров).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Риски и меры по их снижению (примеры для отрасли)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Меры снижения</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Отток квалифицированных кадров за рубеж</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Конкурентная оплата, удалённые/гибридные условия</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13" ht="59" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Отток квалифицированных кадров за рубеж или к конкурентам</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Конкурентная оплата, удалённые/гибридные условия, программы обучения и роста внутри компании</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Зависимость от 1-2 крупных клиентов</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Диверсификация портфеля клиентов</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Валютные риски по контрактам в валюте</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Хеджирование, привязка расчётов к валюте контракта</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Диверсификация портфеля клиентов, не более 30-40% выручки от одного заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Валютные риски по контрактам в иностранной валюте</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Хеджирование, привязка расчётов к валюте контракта, часть резервов в валюте</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Изменение условий налоговых льгот IT Park</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Мониторинг регуляторики, диверсификация юрисдикций для крупных экспортёров</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Рост конкуренции за резидентов и клиентов внутри IT Park</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Узкая специализация/ниша, инвестиции в портфолио и репутацию, а не только цену</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Кибербезопасность и утечка данных клиентов</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Политики безопасности, NDA с сотрудниками, аудит инфраструктуры</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Дополните таблицу своими рисками, специфичными для вашего проекта и региона.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="21">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -851,324 +953,350 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Сумма, сум</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Добавляйте свои строки при необходимости.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Регистрация резидента IT Park</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>налоговые льготы для экспорта IT-услуг</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Рабочие станции и техника</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Лицензии на ПО</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Лицензии на ПО и инструменты разработки</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Сайт / портфолио</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Первый маркетинговый бюджет</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>профили на биржах фриланса/аутсорса, реклама</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Итого: стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="16">
         <f>SUM(B7:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="16" t="n"/>
+      <c r="C12" s="17" t="n"/>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Проекты по договорам</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="B15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>fixed price / time&amp;material</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Подписочная модель (SaaS)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>при продуктовой модели</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Поддержка и сопровождение</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>Консалтинг и аудит существующих систем</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
           <t>Итого: ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B18" s="15">
-        <f>SUM(B15:B17)</f>
+      <c r="B19" s="16">
+        <f>SUM(B15:B18)</f>
         <v/>
       </c>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="C19" s="17" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>ФОТ разработчиков</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="B22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Облачная инфраструктура / хостинг</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Подписки на инструменты разработки</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Маркетинг и продажи (лидогенерация)</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Обучение и развитие команды</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Юридическое и бухгалтерское сопровождение резидента IT Park</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B26" s="15">
-        <f>SUM(B21:B25)</f>
+      <c r="B28" s="16">
+        <f>SUM(B22:B27)</f>
         <v/>
       </c>
-      <c r="C26" s="16" t="n"/>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Ежемесячная прибыль</t>
-        </is>
-      </c>
-      <c r="B28" s="10">
-        <f>B18-B26</f>
-        <v/>
-      </c>
+      <c r="C28" s="17" t="n"/>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Ежемесячная прибыль</t>
+        </is>
+      </c>
+      <c r="B30" s="11">
+        <f>B19-B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Срок выхода на окупаемость, мес.</t>
         </is>
       </c>
-      <c r="B30" s="13">
-        <f>IFERROR(B4/B28,"—")</f>
+      <c r="B32" s="14">
+        <f>IFERROR(B4/B30,"—")</f>
         <v/>
       </c>
-      <c r="C30" s="13">
+      <c r="C32" s="14">
         <f> Начальные инвестиции / Ежемесячная прибыль</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Рентабельность продаж, %</t>
         </is>
       </c>
-      <c r="B31" s="17">
-        <f>IFERROR(B28/B18*100,"—")</f>
+      <c r="B33" s="18">
+        <f>IFERROR(B30/B19*100,"—")</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C33" s="14">
         <f> Ежемесячная прибыль / Выручка × 100%</f>
         <v/>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта.</t>
+    <row r="34"/>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/business-plans/it.xlsx
+++ b/public/business-plans/it.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +126,9 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ФИНАНСОВЫЙ ПЛАН: ИНФОРМАЦИОННЫЕ ТЕХНОЛОГИИ И СВЯЗЬ (IT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>ФИНАНСОВЫЙ ПЛАН: ИНФОРМАЦИОННЫЕ ТЕХНОЛОГИИ И СВЯЗЬ (IT) — ПРИМЕР РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Информационные технологии и связь (IT)» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — только расчётная часть с рабочими формулами.</t>
+          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Информационные технологии и связь (IT)» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — расчётная часть с рабочими формулами, уже заполненная цифрами ПРИМЕРА (иллюстративная компания из резюме бизнес-плана, не реальный заёмщик) — чтобы показать порядок величины и логику расчёта. Перед подачей в банк или инвестору замените суммы на данные своего проекта.</t>
         </is>
       </c>
     </row>
@@ -527,10 +534,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
+          <t>Столбец «Сумма, сум» уже заполнен примером расчёта для иллюстративной компании из этого бизнес-плана — на основе рыночных ориентиров 2025-2026 года (там, где источник известен — со ссылкой в комментарии) или экспертной оценки порядка величины (это тоже отмечено). Итоги, прибыль, срок окупаемости и рентабельность ниже пересчитаются автоматически (это формулы). Замените суммы в столбце B на данные вашего собственного проекта — тогда пересчитается всё.</t>
         </is>
       </c>
     </row>
@@ -541,8 +548,9 @@
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
+      <c r="B7" s="6">
+        <f>B15</f>
+        <v/>
       </c>
     </row>
     <row r="8"/>
@@ -555,66 +563,78 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Регистрация резидента IT Park</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>налоговые льготы для экспорта IT-услуг</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+          <t>налоговые льготы для экспорта IT-услуг — Пример: оценка: юр. сопровождение регистрации ООО и получения статуса резидента IT Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Рабочие станции и техника</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+        <v>140000000</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 6 рабочих мест: 3 MacBook Pro (~28-32 млн/шт., обязательны для iOS-разработки) + 3 ПК/ноутбука (~13-15 млн/шт.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Лицензии на ПО и инструменты разработки</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
+        <v>20000000</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: Apple Developer, Google Play Console, JetBrains, Figma, тестовые устройства на команду</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Сайт / портфолио</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
+        <v>12000000</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка стоимости разработки сайта-портфолио для привлечения европейских заказчиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Первый маркетинговый бюджет</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>профили на биржах фриланса/аутсорса, реклама</t>
+          <t>профили на биржах фриланса/аутсорса, реклама — Пример: оценка: лидогенерация (LinkedIn Ads, Upwork/Clutch, тематические каталоги)</t>
         </is>
       </c>
     </row>
@@ -640,46 +660,50 @@
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="8" t="n"/>
     </row>
-    <row r="18" ht="21" customHeight="1">
+    <row r="18" ht="51" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Проекты по договорам</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0</v>
+        <v>105000000</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>fixed price / time&amp;material</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1">
+          <t>fixed price / time&amp;material — Пример: 2 параллельных проекта, ~5 billable специалистов, блендовая ставка ~$15-20/час, ~150 ч/мес на человека</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Подписочная модель (SaaS)</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>при продуктовой модели</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+          <t>при продуктовой модели — Пример: оценка: небольшой собственный SaaS-продукт на раннем этапе монетизации</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Поддержка и сопровождение</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr"/>
+        <v>15000000</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка выручки от ретейнер-контрактов на поддержку сданных проектов</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -688,9 +712,13 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
+        <v>10000000</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка выручки от разовых консультационных проектов</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -714,49 +742,65 @@
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
     </row>
-    <row r="25" ht="21" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ФОТ разработчиков</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26" ht="21" customHeight="1">
+        <v>86000000</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Пример: тимлид ~18 млн + 4 разработчика ~13 млн каждый (уровень middle, it-park.uz) + QA ~9 млн + PM part-time ~7 млн</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Облачная инфраструктура / хостинг</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
+        <v>4000000</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка расходов на AWS/GCP/CI-CD для нескольких мобильных проектов</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Подписки на инструменты разработки</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <v>4500000</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка ежемесячных подписок (JetBrains, Figma, GitHub, тестовые сервисы)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Маркетинг и продажи (лидогенерация)</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr"/>
+        <v>8500000</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка расходов на лидогенерацию для европейских клиентов</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -765,20 +809,28 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
+        <v>2500000</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка бюджета на курсы/сертификации, помесячно</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Юридическое и бухгалтерское сопровождение резидента IT Park</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr"/>
+        <v>3500000</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка стоимости аутсорс-бухгалтерии и юр. сопровождения статуса резидента</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -815,9 +867,10 @@
         <f>IFERROR(B7/B33,"—")</f>
         <v/>
       </c>
-      <c r="C35" s="9">
-        <f> Начальные инвестиции / Ежемесячная прибыль</f>
-        <v/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Начальные инвестиции ÷ Ежемесячная прибыль</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -830,24 +883,34 @@
         <f>IFERROR(B33/B22*100,"—")</f>
         <v/>
       </c>
-      <c r="C36" s="9">
-        <f> Ежемесячная прибыль / Выручка × 100%</f>
-        <v/>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Ежемесячная прибыль ÷ Выручка × 100%</t>
+        </is>
       </c>
     </row>
     <row r="37"/>
-    <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Как считался этот пример: Сумма стартовых (капитальных) затрат — 204 млн сум; заявленные в резюме 300 млн описывают запас на 3 мес. работы команды (включая ФОТ, который в модели отнесён к ежемесячным расходам, а не к стартовым). При прибыли ≈26 млн сум/мес окупаемость капитальных затрат ≈7,9 мес. — близко к заявленным ~8 мес.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40" ht="55" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Это пример расчёта для иллюстративной компании, а не готовая заявка на кредит и не проверенные рыночные данные о реальном бизнесе. Суммы в столбце B — рабочие формулы: замените их на цифры вашего проекта, и итоги, прибыль, срок окупаемости и рентабельность пересчитаются автоматически. Там, где в комментарии указан источник — это ориентир на 2025-2026 год, проверяйте актуальность перед подачей документов в банк; где указана «экспертная оценка» — это иллюстрация порядка величины, а не факт.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
